--- a/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>MYGN</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44012</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43646</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43281</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42916</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42551</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42185</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41820</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41455</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41090</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>753200</v>
+      </c>
+      <c r="E8" s="3">
         <v>678400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>690600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>299800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>638600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>851100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>743700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>728700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>740500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>723100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>778200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>613200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>496000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>236200</v>
+      </c>
+      <c r="E9" s="3">
         <v>202000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>197600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>91400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>186100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>201000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>177200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>171200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>157300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>147400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>109200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>79600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>64700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E10" s="3">
         <v>476400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>493000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>208400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>452500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>650100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>566500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>557500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>583200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>575700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>669000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>533500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>431300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E12" s="3">
         <v>85400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>81900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>35800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>77200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>68600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>70800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>74400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>75500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>53700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>42600</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -945,29 +961,32 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E14" s="3">
         <v>16900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-76700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>98700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>24100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>17</v>
@@ -984,12 +1003,15 @@
       <c r="N14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1010600</v>
+      </c>
+      <c r="E17" s="3">
         <v>819000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>740600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>387600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>869300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>843500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>621800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>684700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>587100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>588900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>503800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>385200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>315700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-140600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-50000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-87800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-230700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>121900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>44000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>153400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>134200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>274400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>228000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>180300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1147,121 +1179,128 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-500</v>
       </c>
       <c r="F20" s="3">
         <v>-500</v>
       </c>
       <c r="G20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H20" s="3">
         <v>18200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4200</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-197400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-84700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12300</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G21" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="H21" s="3">
         <v>-140500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>85000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>177700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>90500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>183100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>159900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>291700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>242200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>193600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>3200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>17</v>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-262200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-140600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-57100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-94100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-223300</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>120100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>36200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>156000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>134900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>277900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>233300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>184500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-28600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-32600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-23700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>19000</v>
       </c>
       <c r="J24" s="3">
         <v>19000</v>
       </c>
       <c r="K24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="L24" s="3">
         <v>38800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>54700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>101600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>86100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>72400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-112000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-73800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-199600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>101100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>117200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>80200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>176200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>147100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>112200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-199500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>101300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>117200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>80200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>176200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>147100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,32 +1581,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="3">
         <v>-2700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>20700</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>32000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>500</v>
       </c>
       <c r="F32" s="3">
         <v>500</v>
       </c>
       <c r="G32" s="3">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-18200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4200</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-53100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-199500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>133300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>117200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>80200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>176200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>147100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>112200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-53100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-199500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>133300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>117200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>80200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>176200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>147100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>112200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44012</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43646</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43281</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42916</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42551</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42185</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41820</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41455</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41090</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,386 +1987,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E41" s="3">
         <v>56900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>258400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>163700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>93200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>110900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>102400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>64100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>64800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>104100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E42" s="3">
         <v>58000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>81400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>54100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>43700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>69700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>90500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>80700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>121600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>268200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>254200</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114300</v>
+      </c>
+      <c r="E43" s="3">
         <v>101600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>91300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>91500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>71000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>138600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>201600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>95900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>87700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>85100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63100</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E44" s="3">
         <v>20100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>29100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>31400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>34300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>42200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>25100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11600</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E45" s="3">
         <v>38000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>120100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>313600</v>
+      </c>
+      <c r="E46" s="3">
         <v>274600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>484800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>389400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>331700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>348600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>327600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>301700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>314500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>283600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>322400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>484000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>422500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>54800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>37000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>79900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>40600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>84100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>180400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>132700</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>180600</v>
+      </c>
+      <c r="E48" s="3">
         <v>187300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>103000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>58300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>636900</v>
+      </c>
+      <c r="E49" s="3">
         <v>666500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>643300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>905700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>932900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1101900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>773800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>807600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>422800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>369800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>374500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>70200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>72600</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,23 +2479,26 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E52" s="3">
         <v>15500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2300</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>17</v>
@@ -2390,24 +2509,27 @@
       <c r="J52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K52" s="3">
-        <v>5000</v>
+      <c r="K52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L52" s="3">
         <v>5000</v>
       </c>
       <c r="M52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N52" s="3">
         <v>8200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1146500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1198700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1320700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1418800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1404600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1562700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1175300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1208900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>880500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>766200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>823800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>803800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>690600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,50 +2655,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E57" s="3">
         <v>28800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>21100</v>
       </c>
       <c r="L57" s="3">
         <v>21100</v>
       </c>
       <c r="M57" s="3">
+        <v>21100</v>
+      </c>
+      <c r="N57" s="3">
         <v>23100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2609,120 +2742,129 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>130100</v>
+      </c>
+      <c r="E59" s="3">
         <v>108400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>174700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>125400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>125300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>84500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>76200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>195500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>57500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>46400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>155900</v>
+      </c>
+      <c r="E60" s="3">
         <v>137200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>204300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>145900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>147000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>117800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>102200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>217500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>72300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>68700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>64500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>45000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>224800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>224400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>233500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>99100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,51 +2877,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E62" s="3">
         <v>175700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>148600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>167100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>115000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>122500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>97700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>124300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>60100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E66" s="3">
         <v>312900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>352900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>537800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>486400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>473800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>209200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>440500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>132400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>104100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-629500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-366200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-254200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-227000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-173900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>54100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-78200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-73200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-77000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>783200</v>
+      </c>
+      <c r="E76" s="3">
         <v>885800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>967800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>881000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>918200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1088900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>966100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>768400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>748100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>662100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>719000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>728600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>635700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44012</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43646</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43281</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42916</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42551</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42185</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41820</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41455</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41090</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-53100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-199500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>133300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>117200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>80200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>176200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>147100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>112200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E83" s="3">
         <v>52700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>62800</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G83" s="3">
+        <v>35800</v>
+      </c>
+      <c r="H83" s="3">
         <v>72000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>73000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>48300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-110900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-106300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18200</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G89" s="3">
+        <v>-73700</v>
+      </c>
+      <c r="H89" s="3">
         <v>60700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>83700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>115900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>106200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>166300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>140500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>190200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>173900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>141800</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-45300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18000</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="H91" s="3">
         <v>-10200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>274400</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G94" s="3">
+        <v>28000</v>
+      </c>
+      <c r="H94" s="3">
         <v>19300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-286400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-91400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>40900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-75600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-38900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>152900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-150600</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H100" s="3">
         <v>-10000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>182300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-95000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>71800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-68300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-177300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-211800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-80600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-69200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>17</v>
+      <c r="F101" s="3">
+        <v>-600</v>
       </c>
       <c r="G101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4800</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-192400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>141400</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G102" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="H102" s="3">
         <v>70500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>33700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
@@ -971,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>120500</v>
+        <v>112800</v>
       </c>
       <c r="E14" s="3">
         <v>16900</v>

--- a/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>MYGN</t>
   </si>
@@ -736,7 +736,7 @@
         <v>690600</v>
       </c>
       <c r="G8" s="3">
-        <v>299800</v>
+        <v>557000</v>
       </c>
       <c r="H8" s="3">
         <v>638600</v>
@@ -781,7 +781,7 @@
         <v>197600</v>
       </c>
       <c r="G9" s="3">
-        <v>91400</v>
+        <v>178200</v>
       </c>
       <c r="H9" s="3">
         <v>186100</v>
@@ -826,7 +826,7 @@
         <v>493000</v>
       </c>
       <c r="G10" s="3">
-        <v>208400</v>
+        <v>378800</v>
       </c>
       <c r="H10" s="3">
         <v>452500</v>
@@ -890,13 +890,13 @@
         <v>81900</v>
       </c>
       <c r="G12" s="3">
-        <v>35800</v>
+        <v>72900</v>
       </c>
       <c r="H12" s="3">
         <v>77200</v>
       </c>
       <c r="I12" s="3">
-        <v>68600</v>
+        <v>85900</v>
       </c>
       <c r="J12" s="3">
         <v>70800</v>
@@ -971,25 +971,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>112800</v>
+        <v>120000</v>
       </c>
       <c r="E14" s="3">
-        <v>16900</v>
+        <v>4900</v>
       </c>
       <c r="F14" s="3">
-        <v>-76700</v>
+        <v>-76100</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>98700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>24100</v>
-      </c>
-      <c r="J14" s="3" t="s">
+        <v>84100</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-61200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>17</v>
@@ -1016,25 +1016,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>56200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>52700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>62800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>71400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>54400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1010600</v>
+        <v>892100</v>
       </c>
       <c r="E17" s="3">
-        <v>819000</v>
+        <v>814100</v>
       </c>
       <c r="F17" s="3">
-        <v>740600</v>
+        <v>817300</v>
       </c>
       <c r="G17" s="3">
-        <v>387600</v>
+        <v>751800</v>
       </c>
       <c r="H17" s="3">
-        <v>869300</v>
+        <v>770600</v>
       </c>
       <c r="I17" s="3">
         <v>843500</v>
       </c>
       <c r="J17" s="3">
-        <v>621800</v>
+        <v>683000</v>
       </c>
       <c r="K17" s="3">
         <v>684700</v>
@@ -1122,25 +1122,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-257400</v>
+        <v>-138900</v>
       </c>
       <c r="E18" s="3">
-        <v>-140600</v>
+        <v>-135700</v>
       </c>
       <c r="F18" s="3">
-        <v>-50000</v>
+        <v>-126700</v>
       </c>
       <c r="G18" s="3">
         <v>-87800</v>
       </c>
       <c r="H18" s="3">
-        <v>-230700</v>
+        <v>-132000</v>
       </c>
       <c r="I18" s="3">
         <v>7600</v>
       </c>
       <c r="J18" s="3">
-        <v>121900</v>
+        <v>60700</v>
       </c>
       <c r="K18" s="3">
         <v>44000</v>
@@ -1186,25 +1186,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-1900</v>
+        <v>2900</v>
       </c>
       <c r="E20" s="3">
-        <v>3200</v>
+        <v>-600</v>
       </c>
       <c r="F20" s="3">
-        <v>-500</v>
+        <v>600</v>
       </c>
       <c r="G20" s="3">
-        <v>-500</v>
+        <v>-15300</v>
       </c>
       <c r="H20" s="3">
-        <v>18200</v>
+        <v>-600</v>
       </c>
       <c r="I20" s="3">
-        <v>4400</v>
+        <v>-1200</v>
       </c>
       <c r="J20" s="3">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="K20" s="3">
         <v>-1800</v>
@@ -1231,25 +1231,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-197400</v>
+        <v>-85600</v>
       </c>
       <c r="E21" s="3">
-        <v>-84700</v>
+        <v>-82400</v>
       </c>
       <c r="F21" s="3">
-        <v>12300</v>
+        <v>-64500</v>
       </c>
       <c r="G21" s="3">
-        <v>-52500</v>
+        <v>-1100</v>
       </c>
       <c r="H21" s="3">
-        <v>-140500</v>
+        <v>-59400</v>
       </c>
       <c r="I21" s="3">
-        <v>85000</v>
+        <v>81800</v>
       </c>
       <c r="J21" s="3">
-        <v>177700</v>
+        <v>114700</v>
       </c>
       <c r="K21" s="3">
         <v>90500</v>
@@ -1372,10 +1372,10 @@
         <v>-28600</v>
       </c>
       <c r="F24" s="3">
-        <v>-32600</v>
+        <v>-29900</v>
       </c>
       <c r="G24" s="3">
-        <v>-20300</v>
+        <v>-41000</v>
       </c>
       <c r="H24" s="3">
         <v>-23700</v>
@@ -1384,7 +1384,7 @@
         <v>-4400</v>
       </c>
       <c r="J24" s="3">
-        <v>19000</v>
+        <v>-13000</v>
       </c>
       <c r="K24" s="3">
         <v>19000</v>
@@ -1462,10 +1462,10 @@
         <v>-112000</v>
       </c>
       <c r="F26" s="3">
-        <v>-24500</v>
+        <v>-27200</v>
       </c>
       <c r="G26" s="3">
-        <v>-73800</v>
+        <v>-53100</v>
       </c>
       <c r="H26" s="3">
         <v>-199600</v>
@@ -1474,7 +1474,7 @@
         <v>4400</v>
       </c>
       <c r="J26" s="3">
-        <v>101100</v>
+        <v>133100</v>
       </c>
       <c r="K26" s="3">
         <v>17200</v>
@@ -1507,10 +1507,10 @@
         <v>-112000</v>
       </c>
       <c r="F27" s="3">
-        <v>-24500</v>
+        <v>-27200</v>
       </c>
       <c r="G27" s="3">
-        <v>-73800</v>
+        <v>-53100</v>
       </c>
       <c r="H27" s="3">
         <v>-199500</v>
@@ -1519,7 +1519,7 @@
         <v>4600</v>
       </c>
       <c r="J27" s="3">
-        <v>101300</v>
+        <v>133300</v>
       </c>
       <c r="K27" s="3">
         <v>17400</v>
@@ -1590,17 +1590,17 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>17</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>20700</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1900</v>
+        <v>-2900</v>
       </c>
       <c r="E32" s="3">
-        <v>-3200</v>
+        <v>600</v>
       </c>
       <c r="F32" s="3">
-        <v>500</v>
+        <v>-600</v>
       </c>
       <c r="G32" s="3">
-        <v>500</v>
+        <v>15300</v>
       </c>
       <c r="H32" s="3">
-        <v>-18200</v>
+        <v>600</v>
       </c>
       <c r="I32" s="3">
-        <v>-4400</v>
+        <v>1200</v>
       </c>
       <c r="J32" s="3">
-        <v>-1400</v>
+        <v>-400</v>
       </c>
       <c r="K32" s="3">
         <v>1800</v>
@@ -2000,7 +2000,7 @@
         <v>56900</v>
       </c>
       <c r="F41" s="3">
-        <v>258400</v>
+        <v>257400</v>
       </c>
       <c r="G41" s="3">
         <v>117000</v>
@@ -2093,7 +2093,7 @@
         <v>91300</v>
       </c>
       <c r="G43" s="3">
-        <v>91500</v>
+        <v>89500</v>
       </c>
       <c r="H43" s="3">
         <v>71000</v>
@@ -2102,7 +2102,7 @@
         <v>138600</v>
       </c>
       <c r="J43" s="3">
-        <v>201600</v>
+        <v>103300</v>
       </c>
       <c r="K43" s="3">
         <v>95900</v>
@@ -2173,26 +2173,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>36400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>38000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>38400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>120100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>13800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>41700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>9400</v>
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K45" s="3">
         <v>12900</v>
@@ -2263,8 +2263,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E47" s="3">
         <v>54800</v>
@@ -2354,16 +2354,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>636900</v>
+        <v>641500</v>
       </c>
       <c r="E49" s="3">
-        <v>666500</v>
+        <v>673600</v>
       </c>
       <c r="F49" s="3">
-        <v>643300</v>
+        <v>650000</v>
       </c>
       <c r="G49" s="3">
-        <v>905700</v>
+        <v>908000</v>
       </c>
       <c r="H49" s="3">
         <v>932900</v>
@@ -2489,16 +2489,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15400</v>
+        <v>10800</v>
       </c>
       <c r="E52" s="3">
-        <v>15500</v>
+        <v>8400</v>
       </c>
       <c r="F52" s="3">
-        <v>8300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2300</v>
+        <v>1600</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>17</v>
@@ -2707,19 +2707,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>130100</v>
+        <v>38200</v>
       </c>
       <c r="E59" s="3">
-        <v>108400</v>
+        <v>24100</v>
       </c>
       <c r="F59" s="3">
-        <v>174700</v>
+        <v>79000</v>
       </c>
       <c r="G59" s="3">
-        <v>125400</v>
+        <v>49700</v>
       </c>
       <c r="H59" s="3">
-        <v>125300</v>
+        <v>50300</v>
       </c>
       <c r="I59" s="3">
-        <v>84500</v>
+        <v>17700</v>
       </c>
       <c r="J59" s="3">
-        <v>76200</v>
+        <v>12200</v>
       </c>
       <c r="K59" s="3">
         <v>195500</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>38500</v>
+        <v>135900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>130900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>79300</v>
       </c>
       <c r="G61" s="3">
-        <v>224800</v>
+        <v>275400</v>
       </c>
       <c r="H61" s="3">
-        <v>224400</v>
+        <v>281300</v>
       </c>
       <c r="I61" s="3">
         <v>233500</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>168900</v>
+        <v>71500</v>
       </c>
       <c r="E62" s="3">
-        <v>175700</v>
+        <v>44800</v>
       </c>
       <c r="F62" s="3">
-        <v>148600</v>
+        <v>33500</v>
       </c>
       <c r="G62" s="3">
-        <v>167100</v>
+        <v>45200</v>
       </c>
       <c r="H62" s="3">
-        <v>115000</v>
+        <v>31500</v>
       </c>
       <c r="I62" s="3">
-        <v>122500</v>
+        <v>33100</v>
       </c>
       <c r="J62" s="3">
-        <v>97700</v>
+        <v>34400</v>
       </c>
       <c r="K62" s="3">
         <v>124300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>61900</v>
+        <v>13400</v>
       </c>
       <c r="E83" s="3">
-        <v>52700</v>
+        <v>11600</v>
       </c>
       <c r="F83" s="3">
-        <v>62800</v>
+        <v>12100</v>
       </c>
       <c r="G83" s="3">
-        <v>35800</v>
+        <v>10100</v>
       </c>
       <c r="H83" s="3">
-        <v>72000</v>
+        <v>11000</v>
       </c>
       <c r="I83" s="3">
-        <v>73000</v>
+        <v>13700</v>
       </c>
       <c r="J83" s="3">
-        <v>54400</v>
+        <v>17100</v>
       </c>
       <c r="K83" s="3">
         <v>48300</v>
@@ -3971,10 +3971,10 @@
         <v>-106300</v>
       </c>
       <c r="F89" s="3">
-        <v>18200</v>
+        <v>18600</v>
       </c>
       <c r="G89" s="3">
-        <v>-73700</v>
+        <v>-26900</v>
       </c>
       <c r="H89" s="3">
         <v>60700</v>
@@ -4173,7 +4173,7 @@
         <v>274400</v>
       </c>
       <c r="G94" s="3">
-        <v>28000</v>
+        <v>61600</v>
       </c>
       <c r="H94" s="3">
         <v>19300</v>
@@ -4417,7 +4417,7 @@
         <v>-150600</v>
       </c>
       <c r="G100" s="3">
-        <v>-2100</v>
+        <v>-1000</v>
       </c>
       <c r="H100" s="3">
         <v>-10000</v>
@@ -4504,10 +4504,10 @@
         <v>-192400</v>
       </c>
       <c r="F102" s="3">
-        <v>141400</v>
+        <v>141800</v>
       </c>
       <c r="G102" s="3">
-        <v>-46700</v>
+        <v>34800</v>
       </c>
       <c r="H102" s="3">
         <v>70500</v>

--- a/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>MYGN</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44012</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43646</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43281</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42916</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42551</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42185</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41820</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41455</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41090</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>837600</v>
+      </c>
+      <c r="E8" s="3">
         <v>753200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>678400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>690600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>557000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>638600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>851100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>743700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>728700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>740500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>723100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>778200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>613200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>496000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>252200</v>
+      </c>
+      <c r="E9" s="3">
         <v>236200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>202000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>197600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>178200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>186100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>201000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>177200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>171200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>157300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>147400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>109200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>79600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>64700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>585400</v>
+      </c>
+      <c r="E10" s="3">
         <v>517000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>476400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>493000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>378800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>452500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>650100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>566500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>557500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>583200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>575700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>669000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>533500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>431300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E12" s="3">
         <v>88700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>85400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>81900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>72900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>77200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>85900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>70800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>74400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>70600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>75500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>67500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>53700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>42600</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -964,35 +980,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>120000</v>
+        <v>33300</v>
       </c>
       <c r="E14" s="3">
-        <v>4900</v>
+        <v>114300</v>
       </c>
       <c r="F14" s="3">
+        <v>16900</v>
+      </c>
+      <c r="G14" s="3">
         <v>-76100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>84100</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-61200</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>17</v>
@@ -1006,39 +1025,42 @@
       <c r="O14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E15" s="3">
         <v>56200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>52700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>62800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>71400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>72000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>73000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>54400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>892100</v>
+        <v>925600</v>
       </c>
       <c r="E17" s="3">
-        <v>814100</v>
+        <v>897800</v>
       </c>
       <c r="F17" s="3">
+        <v>802100</v>
+      </c>
+      <c r="G17" s="3">
         <v>817300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>751800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>770600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>843500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>683000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>684700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>587100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>588900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>503800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>385200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>315700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-138900</v>
+        <v>-88000</v>
       </c>
       <c r="E18" s="3">
-        <v>-135700</v>
+        <v>-144600</v>
       </c>
       <c r="F18" s="3">
+        <v>-123700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-126700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-87800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-132000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>60700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>44000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>153400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>134200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>274400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>228000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>180300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,130 +1212,137 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4200</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-85600</v>
+        <v>-27900</v>
       </c>
       <c r="E21" s="3">
-        <v>-82400</v>
+        <v>-91300</v>
       </c>
       <c r="F21" s="3">
+        <v>-70400</v>
+      </c>
+      <c r="G21" s="3">
         <v>-64500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-59400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>81800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>114700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>90500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>183100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>159900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>291700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>242200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>193600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E22" s="3">
         <v>2900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>17</v>
@@ -1314,99 +1353,108 @@
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-262200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-140600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-57100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-94100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-223300</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>120100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>156000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>134900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>277900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>233300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>184500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-28600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-29900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-41000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-23700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>54700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>101600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>86100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>72400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-263300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-112000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-53100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-199600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>133100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>117200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>80200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>176200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>147100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>112200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-263300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-53100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-199500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>133300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>117200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>80200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>176200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>147100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>112200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>17</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>17</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-263300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-53100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-199500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>133300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>117200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>80200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>176200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>147100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>112200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-263300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-53100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-199500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>133300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>117200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>80200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>176200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>147100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>112200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44012</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43646</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43281</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42916</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42551</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42185</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41820</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41455</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41090</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,188 +2073,201 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E41" s="3">
         <v>132100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>257400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>163700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>93200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>110900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>102400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>64100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>86400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>8800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>58000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>81400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>33700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>54100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>43700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>69700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>48300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>90500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>80700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>121600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>268200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>254200</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>121200</v>
+      </c>
+      <c r="E43" s="3">
         <v>114300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>91300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>89500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>71000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>138600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>103300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>87700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>85100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>63100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E44" s="3">
         <v>22000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>29100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>31400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>34300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>42200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>25100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11600</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2194,207 +2292,222 @@
       <c r="J45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="3">
         <v>12900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7300</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>298000</v>
+      </c>
+      <c r="E46" s="3">
         <v>313600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>274600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>484800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>389400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>331700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>348600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>327600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>301700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>314500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>283600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>322400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>484000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>422500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3">
         <v>54800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>21000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>37000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>30700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>48500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>79900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>40600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>84100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>180400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>132700</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>172400</v>
+      </c>
+      <c r="E48" s="3">
         <v>180600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>187300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>125300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>103000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>58300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>67200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E49" s="3">
         <v>641500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>673600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>650000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>908000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>932900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1101900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>773800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>807600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>422800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>369800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>374500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>70200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>72600</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,23 +2598,26 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E52" s="3">
         <v>10800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1600</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>17</v>
@@ -2512,24 +2631,27 @@
       <c r="K52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L52" s="3">
-        <v>5000</v>
+      <c r="L52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M52" s="3">
         <v>5000</v>
       </c>
       <c r="N52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O52" s="3">
         <v>8200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>38600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1027600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1146500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1198700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1320700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1418800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1404600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1562700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1175300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1208900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>880500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>766200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>823800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>803800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>690600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,74 +2785,78 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E57" s="3">
         <v>25800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>21100</v>
       </c>
       <c r="M57" s="3">
         <v>21100</v>
       </c>
       <c r="N57" s="3">
+        <v>21100</v>
+      </c>
+      <c r="O57" s="3">
         <v>23100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10100</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E58" s="3">
         <v>16200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2745,129 +2878,138 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E59" s="3">
         <v>38200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>79000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>50300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>195500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>47600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>57500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>46400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>164100</v>
+      </c>
+      <c r="E60" s="3">
         <v>155900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>137200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>204300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>145900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>147000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>117800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>217500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>72300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>68700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>80600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>64500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E61" s="3">
         <v>135900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>130900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>275400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>281300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>233500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>99100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2880,54 +3022,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E62" s="3">
         <v>71500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>44800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>124300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>60100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>35400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>326500</v>
+      </c>
+      <c r="E66" s="3">
         <v>363300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>312900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>352900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>537800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>486400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>473800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>209200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>440500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>132400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-756800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-629500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-366200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-254200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-227000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-173900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>54100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-78200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-73200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-77000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>701100</v>
+      </c>
+      <c r="E76" s="3">
         <v>783200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>885800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>967800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>881000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>918200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1088900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>966100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>768400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>748100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>662100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>719000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>728600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>635700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44012</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43646</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43281</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42916</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42551</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42185</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41820</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41455</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41090</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-263300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-53100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-199500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>133300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>117200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>80200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>176200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>147100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>112200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E83" s="3">
         <v>13400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>48300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-110900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-106300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>60700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>115900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>106200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>166300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>140500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>190200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>173900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>141800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-45300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E94" s="3">
         <v>31900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>274400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>61600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>19300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-286400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-146300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-91400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>40900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-75600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E100" s="3">
         <v>152900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-150600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>182300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>71800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-68300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-177300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-211800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-80600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-600</v>
       </c>
       <c r="F101" s="3">
         <v>-600</v>
       </c>
       <c r="G101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4800</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E102" s="3">
         <v>74500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-192400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>141800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>70500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>33700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
@@ -990,10 +990,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>33300</v>
+        <v>35500</v>
       </c>
       <c r="E14" s="3">
-        <v>114300</v>
+        <v>120000</v>
       </c>
       <c r="F14" s="3">
         <v>16900</v>
@@ -1106,7 +1106,7 @@
         <v>925600</v>
       </c>
       <c r="E17" s="3">
-        <v>897800</v>
+        <v>892100</v>
       </c>
       <c r="F17" s="3">
         <v>802100</v>
@@ -1154,7 +1154,7 @@
         <v>-88000</v>
       </c>
       <c r="E18" s="3">
-        <v>-144600</v>
+        <v>-138900</v>
       </c>
       <c r="F18" s="3">
         <v>-123700</v>
@@ -1219,7 +1219,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>1100</v>
+        <v>-1100</v>
       </c>
       <c r="E20" s="3">
         <v>2900</v>
@@ -1267,10 +1267,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-27900</v>
+        <v>-25700</v>
       </c>
       <c r="E21" s="3">
-        <v>-91300</v>
+        <v>-85600</v>
       </c>
       <c r="F21" s="3">
         <v>-70400</v>
@@ -1795,7 +1795,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1100</v>
+        <v>1100</v>
       </c>
       <c r="E32" s="3">
         <v>-2900</v>

--- a/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>MYGN</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41090</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>824500</v>
+      </c>
+      <c r="E8" s="3">
         <v>837600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>753200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>678400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>690600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>557000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>638600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>851100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>743700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>728700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>740500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>723100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>778200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>613200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>496000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>247900</v>
+      </c>
+      <c r="E9" s="3">
         <v>252200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>236200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>202000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>197600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>178200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>186100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>201000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>177200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>171200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>157300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>147400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>109200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>79600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>64700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>576600</v>
+      </c>
+      <c r="E10" s="3">
         <v>585400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>517000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>476400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>493000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>378800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>452500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>650100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>566500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>557500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>583200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>575700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>669000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>533500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>431300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E12" s="3">
         <v>113400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>88700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>85400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>81900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>72900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>77200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>85900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>74400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>70600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>75500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>67500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>53700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>42600</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -983,38 +999,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>319400</v>
+      </c>
+      <c r="E14" s="3">
         <v>35500</v>
       </c>
-      <c r="E14" s="3">
-        <v>120000</v>
-      </c>
       <c r="F14" s="3">
+        <v>112800</v>
+      </c>
+      <c r="G14" s="3">
         <v>16900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-76100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>84100</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-61200</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>17</v>
@@ -1028,42 +1047,45 @@
       <c r="P14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E15" s="3">
         <v>61200</v>
       </c>
-      <c r="E15" s="3">
-        <v>56200</v>
-      </c>
       <c r="F15" s="3">
+        <v>61900</v>
+      </c>
+      <c r="G15" s="3">
         <v>52700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>62800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>71400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>72000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>73000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>892300</v>
+      </c>
+      <c r="E17" s="3">
         <v>925600</v>
       </c>
-      <c r="E17" s="3">
-        <v>892100</v>
-      </c>
       <c r="F17" s="3">
+        <v>897800</v>
+      </c>
+      <c r="G17" s="3">
         <v>802100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>817300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>751800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>770600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>843500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>683000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>684700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>587100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>588900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>503800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>385200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>315700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-67800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-88000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-138900</v>
-      </c>
       <c r="F18" s="3">
+        <v>-144600</v>
+      </c>
+      <c r="G18" s="3">
         <v>-123700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-126700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-87800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-132000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>60700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>44000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>153400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>134200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>274400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>228000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>180300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1213,139 +1245,146 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>400</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="F20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-25700</v>
       </c>
-      <c r="E21" s="3">
-        <v>-85600</v>
-      </c>
       <c r="F21" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-70400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-64500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-59400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>81800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>114700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>90500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>183100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>159900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>291700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>242200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>193600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>17</v>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-395100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-123500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-262200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-140600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-57100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-94100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-223300</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>120100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>36200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>156000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>134900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>277900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>233300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>184500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-28600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-29900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-41000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-23700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-13000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>54700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>101600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>86100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>72400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-365900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-127300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-263300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-112000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-53100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-199600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>133100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>117200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>80200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>176200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>147100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>112200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-365900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-127300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-263300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-53100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-199500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>133300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>117200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>80200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>176200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>147100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>112200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>17</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>17</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>600</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="F32" s="3">
-        <v>600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>15300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-365900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-127300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-263300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-112000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-53100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-199500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>133300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>80200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>176200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>147100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>112200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-365900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-127300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-263300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-112000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-53100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-199500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>133300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>80200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>176200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>147100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>112200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41090</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E41" s="3">
         <v>102400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>132100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>56900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>257400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>117000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>163700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>110900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>102400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>64800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2131,143 +2220,152 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>8800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>58000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>81400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>54100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>43700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>69700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>48300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>90500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>80700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>121600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>268200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>254200</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E43" s="3">
         <v>121200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>114300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>101600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>91300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>89500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>71000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>138600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>95000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>87700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>85100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>63100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E44" s="3">
         <v>27500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>22000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>27100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>29100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>31400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>34300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>42200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>38300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>25100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11600</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2295,75 +2393,81 @@
       <c r="K45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" s="3">
         <v>12900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7300</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>332600</v>
+      </c>
+      <c r="E46" s="3">
         <v>298000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>313600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>274600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>484800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>389400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>331700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>348600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>327600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>301700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>314500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>283600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>322400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>484000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>422500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2373,141 +2477,150 @@
       <c r="E47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3">
         <v>54800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>37000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>54900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>30700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>48500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>79900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>40600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>84100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>180400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>132700</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E48" s="3">
         <v>172400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>180600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>187300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>103000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>58300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>552100</v>
+        <v>205000</v>
       </c>
       <c r="E49" s="3">
+        <v>548700</v>
+      </c>
+      <c r="F49" s="3">
         <v>641500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>673600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>650000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>908000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>932900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1101900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>773800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>807600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>422800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>369800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>374500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>70200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>72600</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,26 +2717,29 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5100</v>
+        <v>5600</v>
       </c>
       <c r="E52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F52" s="3">
         <v>10800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1600</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>17</v>
@@ -2634,24 +2753,27 @@
       <c r="L52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M52" s="3">
-        <v>5000</v>
+      <c r="M52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N52" s="3">
         <v>5000</v>
       </c>
       <c r="O52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P52" s="3">
         <v>8200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>38600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>706600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1027600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1146500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1198700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1320700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1418800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1404600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1562700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1175300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1208900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>880500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>766200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>823800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>803800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>690600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,80 +2915,84 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E57" s="3">
         <v>32300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>21100</v>
       </c>
       <c r="N57" s="3">
         <v>21100</v>
       </c>
       <c r="O57" s="3">
+        <v>21100</v>
+      </c>
+      <c r="P57" s="3">
         <v>23100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10100</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>12800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2881,138 +3014,147 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>39100</v>
+        <v>25600</v>
       </c>
       <c r="E59" s="3">
+        <v>32500</v>
+      </c>
+      <c r="F59" s="3">
         <v>38200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>195500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>47600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>57500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E60" s="3">
         <v>164100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>155900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>137200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>204300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>145900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>147000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>117800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>102200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>217500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>72300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>68700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>80600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>64500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>45000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>202900</v>
+      </c>
+      <c r="E61" s="3">
         <v>127500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>135900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>130900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>275400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>281300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>233500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>99100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3025,57 +3167,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>34900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>71500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>44800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>124300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>60100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>338600</v>
+      </c>
+      <c r="E66" s="3">
         <v>326500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>363300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>312900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>352900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>537800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>486400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>473800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>209200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>440500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>132400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>104800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1122700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-756800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-629500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-366200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-254200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-227000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-173900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>54100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E76" s="3">
         <v>701100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>783200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>885800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>967800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>881000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>918200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1088900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>966100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>768400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>748100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>662100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>719000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>728600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>635700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41090</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-365900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-127300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-263300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-112000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-53100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-199500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>133300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>80200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>176200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>147100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>112200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E83" s="3">
         <v>19100</v>
       </c>
-      <c r="E83" s="3">
-        <v>13400</v>
-      </c>
       <c r="F83" s="3">
+        <v>19100</v>
+      </c>
+      <c r="G83" s="3">
         <v>11600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>48300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-110900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-106300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-26900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>83700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>115900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>106200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>166300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>140500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>190200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>173900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>141800</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>31900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-77500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>274400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>61600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-286400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-146300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-91400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>40900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-75600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-38900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>152900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-150600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>182300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-95000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>71800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-68300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-177300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-211800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-80600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-69200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-600</v>
       </c>
       <c r="G101" s="3">
         <v>-600</v>
       </c>
       <c r="H101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4800</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>74500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-192400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>141800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>70500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>33700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
